--- a/examples/excel/charts.xlsx
+++ b/examples/excel/charts.xlsx
@@ -3,9 +3,9 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="Analysis" sheetId="2" r:id="R2db11f37d59a49d6"/>
-    <x:sheet name="StockData" sheetId="3" r:id="R7a596fc7efd2401b"/>
-    <x:sheet name="Assessment" sheetId="4" r:id="R2dff24d9725349a6"/>
+    <x:sheet name="Analysis" sheetId="2" r:id="Rb6072b1ba3eb4df9"/>
+    <x:sheet name="StockData" sheetId="3" r:id="Re0f7873769744b44"/>
+    <x:sheet name="Assessment" sheetId="4" r:id="Rb4649b6ee473439f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1825,7 +1825,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R8aa6a3c3fbda4eda"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R862a8633a8a844d9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1855,7 +1855,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rf546dfa5dfe4441c"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R362fd87a32c44909"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1885,7 +1885,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Ra8274f169729443f"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R11a3688d26e14787"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1915,7 +1915,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R63b5e80eec464537"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R7210dec1daca4db2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1950,7 +1950,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rc2c126b06bdc4b10"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R6f313a028861415f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1980,7 +1980,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R104f8ac61bb245fb"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R4caa4257730b4aed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2015,7 +2015,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R6e17a72024e1448b"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rfac269e8bb84429b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2050,7 +2050,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="R006d030d87004d66"/>
+          <c:chart xmlns:p5="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" p5:id="Rdc457f110c054664"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2323,7 +2323,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07dbeb937e1d44d8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4925c3cef0e64295"/>
 </x:worksheet>
 </file>
 
@@ -2555,7 +2555,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R292b805f1e244275"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a556a014e174a2f"/>
 </x:worksheet>
 </file>
 
@@ -2983,7 +2983,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb49ea258636e4eca"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c81da26fe24bc9"/>
 </x:worksheet>
 </file>
 
@@ -3117,6 +3117,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1da0d769c824469d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a49207658cb4c4a"/>
 </x:worksheet>
 </file>